--- a/04-northbridge-cloudworks-grc-program/05-soc2-readiness/artifacts/Northbridge-SOC2-Readiness-and-Evidence-Tracker.xlsx
+++ b/04-northbridge-cloudworks-grc-program/05-soc2-readiness/artifacts/Northbridge-SOC2-Readiness-and-Evidence-Tracker.xlsx
@@ -12,13 +12,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Dashboard'!$A$1:$H$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Control Matrix'!$A$1:$I$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Dashboard'!$A$1:$H$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Control Matrix'!$A$1:$J$23</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'PBC Tracker'!$A$1:$H$11</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Audit Findings'!$A$1:$I$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Remediation Tracker'!$A$1:$H$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Readiness Report'!$A$1:$D$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'References'!$A$1:$C$11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'References'!$A$1:$C$12</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -239,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -347,6 +347,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -839,7 +842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -910,14 +913,17 @@
           <t>Access Control</t>
         </is>
       </c>
-      <c r="E4" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" s="30" t="n">
-        <v>0</v>
+      <c r="E4" s="30">
+        <f>COUNTIFS('Control Matrix'!$J$2:$J$23,$D4,'Control Matrix'!$G$2:$G$23,E$3)</f>
+        <v/>
+      </c>
+      <c r="F4" s="30">
+        <f>COUNTIFS('Control Matrix'!$J$2:$J$23,$D4,'Control Matrix'!$G$2:$G$23,F$3)</f>
+        <v/>
+      </c>
+      <c r="G4" s="30">
+        <f>COUNTIFS('Control Matrix'!$J$2:$J$23,$D4,'Control Matrix'!$G$2:$G$23,G$3)</f>
+        <v/>
       </c>
       <c r="H4" s="30" t="inlineStr">
         <is>
@@ -940,14 +946,17 @@
           <t>Security Operations</t>
         </is>
       </c>
-      <c r="E5" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" s="31" t="n">
-        <v>1</v>
+      <c r="E5" s="31">
+        <f>COUNTIFS('Control Matrix'!$J$2:$J$23,$D5,'Control Matrix'!$G$2:$G$23,E$3)</f>
+        <v/>
+      </c>
+      <c r="F5" s="31">
+        <f>COUNTIFS('Control Matrix'!$J$2:$J$23,$D5,'Control Matrix'!$G$2:$G$23,F$3)</f>
+        <v/>
+      </c>
+      <c r="G5" s="31">
+        <f>COUNTIFS('Control Matrix'!$J$2:$J$23,$D5,'Control Matrix'!$G$2:$G$23,G$3)</f>
+        <v/>
       </c>
       <c r="H5" s="31" t="inlineStr">
         <is>
@@ -970,14 +979,17 @@
           <t>Availability</t>
         </is>
       </c>
-      <c r="E6" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="31" t="n">
-        <v>0</v>
+      <c r="E6" s="31">
+        <f>COUNTIFS('Control Matrix'!$J$2:$J$23,$D6,'Control Matrix'!$G$2:$G$23,E$3)</f>
+        <v/>
+      </c>
+      <c r="F6" s="31">
+        <f>COUNTIFS('Control Matrix'!$J$2:$J$23,$D6,'Control Matrix'!$G$2:$G$23,F$3)</f>
+        <v/>
+      </c>
+      <c r="G6" s="31">
+        <f>COUNTIFS('Control Matrix'!$J$2:$J$23,$D6,'Control Matrix'!$G$2:$G$23,G$3)</f>
+        <v/>
       </c>
       <c r="H6" s="31" t="inlineStr">
         <is>
@@ -1000,14 +1012,17 @@
           <t>Vendor / Cloud</t>
         </is>
       </c>
-      <c r="E7" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" s="31" t="n">
-        <v>0</v>
+      <c r="E7" s="31">
+        <f>COUNTIFS('Control Matrix'!$J$2:$J$23,$D7,'Control Matrix'!$G$2:$G$23,E$3)</f>
+        <v/>
+      </c>
+      <c r="F7" s="31">
+        <f>COUNTIFS('Control Matrix'!$J$2:$J$23,$D7,'Control Matrix'!$G$2:$G$23,F$3)</f>
+        <v/>
+      </c>
+      <c r="G7" s="31">
+        <f>COUNTIFS('Control Matrix'!$J$2:$J$23,$D7,'Control Matrix'!$G$2:$G$23,G$3)</f>
+        <v/>
       </c>
       <c r="H7" s="31" t="inlineStr">
         <is>
@@ -1030,14 +1045,17 @@
           <t>Governance / Evidence</t>
         </is>
       </c>
-      <c r="E8" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="G8" s="32" t="n">
-        <v>0</v>
+      <c r="E8" s="32">
+        <f>COUNTIFS('Control Matrix'!$J$2:$J$23,$D8,'Control Matrix'!$G$2:$G$23,E$3)</f>
+        <v/>
+      </c>
+      <c r="F8" s="32">
+        <f>COUNTIFS('Control Matrix'!$J$2:$J$23,$D8,'Control Matrix'!$G$2:$G$23,F$3)</f>
+        <v/>
+      </c>
+      <c r="G8" s="32">
+        <f>COUNTIFS('Control Matrix'!$J$2:$J$23,$D8,'Control Matrix'!$G$2:$G$23,G$3)</f>
+        <v/>
       </c>
       <c r="H8" s="32" t="inlineStr">
         <is>
@@ -1052,7 +1070,30 @@
         </is>
       </c>
       <c r="B9" s="38" t="n">
-        <v>46247</v>
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E10">
+        <f>SUM(E4:E8)</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>SUM(F4:F8)</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>SUM(G4:G8)</f>
+        <v/>
+      </c>
+      <c r="H10" s="15">
+        <f>SUM(E10:G10)&amp;" controls; matches overall: "&amp;IF(SUM(E10:G10)=B3,"Yes","No")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1070,7 +1111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1082,9 +1123,10 @@
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="27" t="inlineStr">
         <is>
           <t>Control ID</t>
@@ -1125,9 +1167,14 @@
           <t>Evidence Needed</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
-        <is>
-          <t>Risk Tier</t>
+      <c r="I1" s="43" t="inlineStr">
+        <is>
+          <t>Evidence Review Priority</t>
+        </is>
+      </c>
+      <c r="J1" s="29" t="inlineStr">
+        <is>
+          <t>Readiness Area</t>
         </is>
       </c>
     </row>
@@ -1177,6 +1224,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J2" s="30" t="inlineStr">
+        <is>
+          <t>Access Control</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="31" t="inlineStr">
@@ -1224,6 +1276,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J3" s="31" t="inlineStr">
+        <is>
+          <t>Access Control</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -1271,6 +1328,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J4" s="31" t="inlineStr">
+        <is>
+          <t>Access Control</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="31" t="inlineStr">
@@ -1318,6 +1380,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J5" s="31" t="inlineStr">
+        <is>
+          <t>Security Operations</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="31" t="inlineStr">
@@ -1365,6 +1432,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J6" s="31" t="inlineStr">
+        <is>
+          <t>Security Operations</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="31" t="inlineStr">
@@ -1412,6 +1484,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J7" s="31" t="inlineStr">
+        <is>
+          <t>Security Operations</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="31" t="inlineStr">
@@ -1459,6 +1536,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J8" s="31" t="inlineStr">
+        <is>
+          <t>Security Operations</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
@@ -1506,6 +1588,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J9" s="31" t="inlineStr">
+        <is>
+          <t>Security Operations</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
@@ -1553,6 +1640,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J10" s="31" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="31" t="inlineStr">
@@ -1600,6 +1692,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J11" s="31" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="31" t="inlineStr">
@@ -1647,6 +1744,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J12" s="31" t="inlineStr">
+        <is>
+          <t>Vendor / Cloud</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="31" t="inlineStr">
@@ -1694,6 +1796,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J13" s="31" t="inlineStr">
+        <is>
+          <t>Security Operations</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="31" t="inlineStr">
@@ -1741,6 +1848,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J14" s="31" t="inlineStr">
+        <is>
+          <t>Governance / Evidence</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="31" t="inlineStr">
@@ -1788,6 +1900,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J15" s="31" t="inlineStr">
+        <is>
+          <t>Governance / Evidence</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="31" t="inlineStr">
@@ -1835,6 +1952,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J16" s="31" t="inlineStr">
+        <is>
+          <t>Governance / Evidence</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
@@ -1882,6 +2004,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J17" s="31" t="inlineStr">
+        <is>
+          <t>Vendor / Cloud</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="31" t="inlineStr">
@@ -1929,6 +2056,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J18" s="31" t="inlineStr">
+        <is>
+          <t>Governance / Evidence</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="31" t="inlineStr">
@@ -1976,6 +2108,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J19" s="31" t="inlineStr">
+        <is>
+          <t>Governance / Evidence</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="31" t="inlineStr">
@@ -2023,6 +2160,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J20" s="31" t="inlineStr">
+        <is>
+          <t>Governance / Evidence</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="31" t="inlineStr">
@@ -2070,6 +2212,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J21" s="31" t="inlineStr">
+        <is>
+          <t>Governance / Evidence</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="31" t="inlineStr">
@@ -2117,6 +2264,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J22" s="31" t="inlineStr">
+        <is>
+          <t>Governance / Evidence</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="32" t="inlineStr">
@@ -2162,6 +2314,11 @@
       <c r="I23" s="32" t="inlineStr">
         <is>
           <t>Medium</t>
+        </is>
+      </c>
+      <c r="J23" s="32" t="inlineStr">
+        <is>
+          <t>Governance / Evidence</t>
         </is>
       </c>
     </row>
@@ -2182,6 +2339,11 @@
     <cfRule type="containsText" priority="11" operator="containsText" dxfId="0" text="Exception"/>
     <cfRule type="containsText" priority="12" operator="containsText" dxfId="1" text="Partial"/>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="J2:J23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Choose one readiness area" error="Use one of the five dashboard areas." type="list" errorStyle="stop">
+      <formula1>"Access Control,Security Operations,Availability,Vendor / Cloud,Governance / Evidence"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -3432,7 +3594,7 @@
         </is>
       </c>
       <c r="B10" s="41" t="n">
-        <v>46247</v>
+        <v>46275</v>
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
@@ -3460,7 +3622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3655,6 +3817,23 @@
         </is>
       </c>
     </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>Scenario dates and rating definitions</t>
+        </is>
+      </c>
+      <c r="B12" s="32" t="inlineStr">
+        <is>
+          <t>Fictional assessment assumptions; see shared company profile</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>../../00-company-profile/Northbridge-Company-and-GRC-Scope.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
